--- a/shop-main/Dalaila Botique/dalaila satement/MAIN.xlsx
+++ b/shop-main/Dalaila Botique/dalaila satement/MAIN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shop-main\shop-main\Dalaila Botique\dalaila satement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B5456D-D0A0-47E2-9E93-C3909F3950AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24136989-28E6-4308-81BF-26C5CC3BF32E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5640" xr2:uid="{AFF0AB6C-1450-46AA-A0E4-B4A4A7173A68}"/>
   </bookViews>
@@ -117,10 +117,10 @@
     <t>October,2022</t>
   </si>
   <si>
-    <t>November,202</t>
-  </si>
-  <si>
     <t>August,2022</t>
+  </si>
+  <si>
+    <t>November,2022</t>
   </si>
 </sst>
 </file>
@@ -786,7 +786,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="2">
         <v>54506</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="2">
         <v>36947</v>
